--- a/resources/config.xlsx
+++ b/resources/config.xlsx
@@ -34,7 +34,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PT11S</t>
+          <t>PT10S</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>

--- a/resources/config.xlsx
+++ b/resources/config.xlsx
@@ -34,29 +34,61 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PT10S</t>
+          <t>PT1S</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>x_axis_label</t>
+          <t>history_range</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>PT12M30S</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>max_redraw_hz</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>200.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>max_plot_points</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>1700000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>x_axis_label</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>y_axis_label</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>y</t>
         </is>
@@ -183,25 +215,30 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>show_dots</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>host</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>port</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>device_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>attribute_name</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>polling_interval_msec</t>
         </is>
@@ -226,25 +263,28 @@
       <c r="D2">
         <v>1.0</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>127.0.0.1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>10000</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>test/power_supply/1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>temp_modulator_transistors_float</t>
         </is>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>10</v>
       </c>
     </row>
@@ -261,31 +301,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cyan</t>
+          <t>cadetblue</t>
         </is>
       </c>
       <c r="D3">
         <v>1.0</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>127.0.0.1</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>10000</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>test/power_supply/1</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>temp_inductor_float</t>
         </is>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>20</v>
       </c>
     </row>
@@ -308,25 +351,28 @@
       <c r="D4">
         <v>3.0</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>10.10.0.34</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>10000</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>MR/DIAG/bpm12</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>SaX</t>
         </is>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>2</v>
       </c>
     </row>
@@ -360,6 +406,11 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>show_dots</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>polling_interval_msec</t>
         </is>
       </c>
@@ -378,8 +429,11 @@
       <c r="D2">
         <v>1.0</v>
       </c>
-      <c r="E2">
-        <v>5</v>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -412,45 +466,50 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>show_dots</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>host</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>port</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>modbus_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>register_type</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>register_address</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>data_type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>polling_interval_msec</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>byte_order</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>word_order</t>
         </is>
@@ -475,39 +534,42 @@
       <c r="D2">
         <v>2.0</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>45.8.248.56</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>502</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>6</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>holding</t>
         </is>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>float32</t>
         </is>
       </c>
-      <c r="K2">
-        <v>60</v>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2">
+        <v>100</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>big</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>big</t>
         </is>
@@ -532,39 +594,42 @@
       <c r="D3">
         <v>1.0</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>10.10.9.101</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>502</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>input</t>
         </is>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>6</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>float32</t>
         </is>
       </c>
-      <c r="K3">
-        <v>11</v>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3">
+        <v>100</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>little</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>big</t>
         </is>

--- a/resources/config.xlsx
+++ b/resources/config.xlsx
@@ -34,7 +34,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PT1S</t>
+          <t>PT5S</t>
         </is>
       </c>
     </row>
@@ -57,7 +57,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>200.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="5">
@@ -67,7 +67,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>1700000</v>
+        <v>9999999</v>
       </c>
     </row>
     <row r="6">

--- a/resources/config.xlsx
+++ b/resources/config.xlsx
@@ -46,7 +46,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PT12M30S</t>
+          <t>PT1M40S</t>
         </is>
       </c>
     </row>
@@ -92,6 +92,76 @@
         <is>
           <t>y</t>
         </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>anomaly_z_score_enabled</t>
+        </is>
+      </c>
+      <c r="B8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>anomaly_z_score_threshold</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>anomaly_z_score_window_size</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>anomaly_z_score_min_points</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>anomaly_delta_jump_enabled</t>
+        </is>
+      </c>
+      <c r="B12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>anomaly_delta_jump_threshold</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>anomaly_delta_jump_min_points</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/resources/config.xlsx
+++ b/resources/config.xlsx
@@ -34,7 +34,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PT5S</t>
+          <t>PT7S</t>
         </is>
       </c>
     </row>
@@ -141,7 +141,7 @@
         </is>
       </c>
       <c r="B12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -331,7 +331,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
